--- a/results/detailed_report_vem2.xlsx
+++ b/results/detailed_report_vem2.xlsx
@@ -473,13 +473,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.247622046901114e-11</v>
+        <v>2.24762225675044e-11</v>
       </c>
       <c r="E2" t="n">
         <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4486187000002246</v>
+        <v>0.1838165999979537</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.948902576636929e-09</v>
+        <v>4.948902783336852e-09</v>
       </c>
       <c r="E3" t="n">
         <v>3589</v>
       </c>
       <c r="F3" t="n">
-        <v>56.79556529999991</v>
+        <v>28.99850700000025</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.798760970828371e-09</v>
+        <v>3.798761123960302e-09</v>
       </c>
       <c r="E4" t="n">
         <v>4696</v>
       </c>
       <c r="F4" t="n">
-        <v>26.3757499000003</v>
+        <v>11.48162769999908</v>
       </c>
     </row>
     <row r="5">
@@ -539,13 +539,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.964171889719481e-09</v>
+        <v>4.964172146079388e-09</v>
       </c>
       <c r="E5" t="n">
         <v>7174</v>
       </c>
       <c r="F5" t="n">
-        <v>386.4390162</v>
+        <v>224.2007552000032</v>
       </c>
     </row>
     <row r="6">
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.299983347370591e-09</v>
+        <v>4.299983332140616e-09</v>
       </c>
       <c r="E6" t="n">
         <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3975447999991957</v>
+        <v>0.2094176000027801</v>
       </c>
     </row>
     <row r="7">
@@ -583,13 +583,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.958369587755855e-07</v>
+        <v>4.958369589175199e-07</v>
       </c>
       <c r="E7" t="n">
         <v>2714</v>
       </c>
       <c r="F7" t="n">
-        <v>42.0966726000006</v>
+        <v>21.81571139999869</v>
       </c>
     </row>
     <row r="8">
@@ -605,13 +605,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.80985054609981e-07</v>
+        <v>3.809850547631133e-07</v>
       </c>
       <c r="E8" t="n">
         <v>3566</v>
       </c>
       <c r="F8" t="n">
-        <v>21.99656440000035</v>
+        <v>9.096856199998001</v>
       </c>
     </row>
     <row r="9">
@@ -627,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4.965607769045873e-07</v>
+        <v>4.965607771164741e-07</v>
       </c>
       <c r="E9" t="n">
         <v>5425</v>
       </c>
       <c r="F9" t="n">
-        <v>294.8649671000003</v>
+        <v>175.3562974999986</v>
       </c>
     </row>
     <row r="10">
@@ -649,13 +649,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4.74299628233515e-07</v>
+        <v>4.742996282507406e-07</v>
       </c>
       <c r="E10" t="n">
         <v>56</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3813907000003383</v>
+        <v>0.1677825000006123</v>
       </c>
     </row>
     <row r="11">
@@ -671,13 +671,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.941761267321043e-05</v>
+        <v>4.941761267332614e-05</v>
       </c>
       <c r="E11" t="n">
         <v>1840</v>
       </c>
       <c r="F11" t="n">
-        <v>29.69186530000025</v>
+        <v>31.30302099999972</v>
       </c>
     </row>
     <row r="12">
@@ -693,13 +693,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.791418977698653e-05</v>
+        <v>3.791418977713903e-05</v>
       </c>
       <c r="E12" t="n">
         <v>2438</v>
       </c>
       <c r="F12" t="n">
-        <v>14.9082212000003</v>
+        <v>6.681042399999569</v>
       </c>
     </row>
     <row r="13">
@@ -715,13 +715,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.967034430857491e-05</v>
+        <v>4.967034430877752e-05</v>
       </c>
       <c r="E13" t="n">
         <v>3676</v>
       </c>
       <c r="F13" t="n">
-        <v>194.0988326000006</v>
+        <v>130.5803974000009</v>
       </c>
     </row>
     <row r="14">
@@ -737,13 +737,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.729017222225196e-05</v>
+        <v>5.729017222227324e-05</v>
       </c>
       <c r="E14" t="n">
         <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2676563999993959</v>
+        <v>0.1320744000004197</v>
       </c>
     </row>
     <row r="15">
@@ -759,13 +759,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.004951189291541634</v>
+        <v>0.004951189291541739</v>
       </c>
       <c r="E15" t="n">
         <v>965</v>
       </c>
       <c r="F15" t="n">
-        <v>14.50376460000007</v>
+        <v>8.653061899996828</v>
       </c>
     </row>
     <row r="16">
@@ -781,13 +781,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003811929529387815</v>
+        <v>0.003811929529387903</v>
       </c>
       <c r="E16" t="n">
         <v>1308</v>
       </c>
       <c r="F16" t="n">
-        <v>7.502474399999301</v>
+        <v>3.69882239999788</v>
       </c>
     </row>
     <row r="17">
@@ -803,13 +803,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.004968461406190458</v>
+        <v>0.004968461406190592</v>
       </c>
       <c r="E17" t="n">
         <v>1927</v>
       </c>
       <c r="F17" t="n">
-        <v>96.87882140000056</v>
+        <v>69.62509730000238</v>
       </c>
     </row>
   </sheetData>

--- a/results/detailed_report_vem2.xlsx
+++ b/results/detailed_report_vem2.xlsx
@@ -479,7 +479,7 @@
         <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1838165999979537</v>
+        <v>0.2642046999972081</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         <v>3589</v>
       </c>
       <c r="F3" t="n">
-        <v>28.99850700000025</v>
+        <v>62.32910199999969</v>
       </c>
     </row>
     <row r="4">
@@ -523,7 +523,7 @@
         <v>4696</v>
       </c>
       <c r="F4" t="n">
-        <v>11.48162769999908</v>
+        <v>13.84018469999864</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>7174</v>
       </c>
       <c r="F5" t="n">
-        <v>224.2007552000032</v>
+        <v>295.6419326999967</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2094176000027801</v>
+        <v>0.1990863000028185</v>
       </c>
     </row>
     <row r="7">
@@ -589,7 +589,7 @@
         <v>2714</v>
       </c>
       <c r="F7" t="n">
-        <v>21.81571139999869</v>
+        <v>40.90166409999802</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         <v>3566</v>
       </c>
       <c r="F8" t="n">
-        <v>9.096856199998001</v>
+        <v>11.07074549999743</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +633,7 @@
         <v>5425</v>
       </c>
       <c r="F9" t="n">
-        <v>175.3562974999986</v>
+        <v>211.6369372000008</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         <v>56</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1677825000006123</v>
+        <v>0.1864691999999195</v>
       </c>
     </row>
     <row r="11">
@@ -677,7 +677,7 @@
         <v>1840</v>
       </c>
       <c r="F11" t="n">
-        <v>31.30302099999972</v>
+        <v>34.48241269999926</v>
       </c>
     </row>
     <row r="12">
@@ -699,7 +699,7 @@
         <v>2438</v>
       </c>
       <c r="F12" t="n">
-        <v>6.681042399999569</v>
+        <v>7.396072800000184</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
         <v>3676</v>
       </c>
       <c r="F13" t="n">
-        <v>130.5803974000009</v>
+        <v>153.2921692</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +743,7 @@
         <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1320744000004197</v>
+        <v>0.1493538999984594</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         <v>965</v>
       </c>
       <c r="F15" t="n">
-        <v>8.653061899996828</v>
+        <v>17.5719136000007</v>
       </c>
     </row>
     <row r="16">
@@ -787,7 +787,7 @@
         <v>1308</v>
       </c>
       <c r="F16" t="n">
-        <v>3.69882239999788</v>
+        <v>4.042688999999882</v>
       </c>
     </row>
     <row r="17">
@@ -809,7 +809,7 @@
         <v>1927</v>
       </c>
       <c r="F17" t="n">
-        <v>69.62509730000238</v>
+        <v>84.84626200000093</v>
       </c>
     </row>
   </sheetData>
